--- a/Thread Chart/The Sourcing Department Thread Charts.xlsx
+++ b/Thread Chart/The Sourcing Department Thread Charts.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\The Sourcing Department\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C59A202-3496-4D6E-8CDA-6AD67A3948DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82EC714A-7A48-41EA-AFFD-8B29948389AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{3D6BC03A-EED6-459C-97BA-FAB84E35F479}"/>
+    <workbookView xWindow="19090" yWindow="-5720" windowWidth="38620" windowHeight="21100" xr2:uid="{3D6BC03A-EED6-459C-97BA-FAB84E35F479}"/>
   </bookViews>
   <sheets>
     <sheet name="Madeira Polyneon" sheetId="1" r:id="rId1"/>
     <sheet name="Madeira Classic Rayon " sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Madeira Classic Rayon '!$A$2:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Madeira Classic Rayon '!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Madeira Polyneon'!$A$1:$I$27</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -118,17 +118,17 @@
     <t>Yellows</t>
   </si>
   <si>
+    <t>Red</t>
+  </si>
+  <si>
     <t>Madeira Classic</t>
-  </si>
-  <si>
-    <t>Red</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,8 +743,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC3CE04-1F73-40AA-924C-F40F56294D6D}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
@@ -752,14 +752,14 @@
     <col min="4" max="4" width="19.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="2" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="2"/>
-    <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="2"/>
-    <col min="15" max="15" width="50.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="2"/>
+    <col min="7" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -788,7 +788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -815,7 +815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -842,7 +842,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -869,7 +869,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -896,7 +896,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -923,7 +923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -950,7 +950,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -977,7 +977,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="52.5" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -1491,7 +1491,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="c1+wKMl7VqiCHjfKG5+fpBDU+kEbxoAtVeMNzhiOdwYsvPsiVgz93yshndqrmE5wBNN6QESKvuQ4OP0i8NI4Nw==" saltValue="WltbNfM4diuSt2tTXqpDrg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange sqref="A1:I27" name="AllowSortFilter"/>
   </protectedRanges>
@@ -1502,8 +1502,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6332F9E0-86FF-4108-A557-29A9444F4085}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
@@ -1511,14 +1511,14 @@
     <col min="4" max="4" width="19.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="2" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="2"/>
-    <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="2"/>
-    <col min="15" max="15" width="50.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="2"/>
+    <col min="7" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1547,15 +1547,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D2" s="2">
         <v>1147</v>
@@ -1575,11 +1575,232 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TzHDfyl5eYXdbFK5OnjLUJiJNPs43Uhy38FwxLVvVb4iJPRlRofmAbh3LNWmWcK/Zr6QU27voN0BuhAa25klxg==" saltValue="NupHLavsSj7itaMrNMAY8w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange sqref="A1:I2" name="AllowSortFilter"/>
   </protectedRanges>
-  <autoFilter ref="A2:I2" xr:uid="{6332F9E0-86FF-4108-A557-29A9444F4085}"/>
+  <autoFilter ref="A1:I1" xr:uid="{6332F9E0-86FF-4108-A557-29A9444F4085}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49F2C427-A94E-41F3-953B-9AB47C608FB7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0188CC3-234B-49E5-B368-C82281D40550}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79D73659-63D9-433E-8F80-C1E5B93628A0}"/>
 </file>